--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_rf_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_rf_yearly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>1.152765466596319</v>
       </c>
       <c r="AD3" s="3" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>3/7</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2/7</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>3/6</t>
-        </is>
-      </c>
-      <c r="AF3" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AH3" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2/5</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1040,27 +1041,27 @@
         <v>0.8699837092823588</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
@@ -1068,7 +1069,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1076,15 +1077,15 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1189,51 +1190,51 @@
         <v>0.4537003899104692</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1342,75 +1343,75 @@
         <v>0.8795619781566564</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -1509,51 +1510,51 @@
         <v>1.093526307450448</v>
       </c>
       <c r="AD7" s="3" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2/7</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>3/7</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2/7</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>2/7</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>2/6</t>
-        </is>
-      </c>
-      <c r="AF7" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AH7" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="AJ7" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AN7" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>2/5</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1662,75 +1663,75 @@
         <v>1.093526307450448</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AP8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AR8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
     </row>
@@ -1829,51 +1830,51 @@
         <v>0.9111145168994106</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>4/6</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>3/5</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -1982,43 +1983,43 @@
         <v>1.063307876926229</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH10" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN10" s="3" t="n">
@@ -2026,31 +2027,31 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AP10" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR10" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AT10" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
     </row>
@@ -2349,66 +2350,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791227</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.2657575172078715</v>
+        <v>0.09032004823014485</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.2657575172078715</v>
+        <v>0.04076898034342919</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582908814</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791227</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493449</v>
+        <v>0.204425521991354</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2456,66 +2459,68 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>36105</v>
+      </c>
       <c r="M3" t="n">
-        <v>1896</v>
+        <v>79</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.5165540962256929</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="P3" t="n">
-        <v>1894</v>
+        <v>77</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.2945323051586157</v>
+        <v>0.09791080322851566</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.2945323051586157</v>
+        <v>0.04238006996766621</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>-0.03477373878520784</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.5165540962256929</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1258</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1.068483758354155</v>
+        <v>0.2136042609009934</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2523,9 +2528,11 @@
       <c r="AG3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
       <c r="AI3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
       <c r="AK3" s="3" t="inlineStr"/>
@@ -2569,34 +2576,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>38028</v>
+        <v>36105</v>
       </c>
       <c r="M4" t="n">
-        <v>975</v>
+        <v>79</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="P4" t="n">
-        <v>786</v>
+        <v>78</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1468876731549894</v>
+        <v>0.08993390447450868</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.1053602020059354</v>
+        <v>0.03892731995262652</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -2606,39 +2613,43 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>392</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4219409803207652</v>
+        <v>0.1946904599376615</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.1891721031526803</v>
+        <v>-0.003452750015039689</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.2198181654379168</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>0.01304506736727939</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -2690,34 +2701,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36880</v>
+        <v>36038</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>39192</v>
+        <v>36105</v>
       </c>
       <c r="M5" t="n">
-        <v>1777</v>
+        <v>79</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2224002232436589</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.2317017928095088</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="P5" t="n">
-        <v>1774</v>
+        <v>77</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1741963661382502</v>
+        <v>0.09791080322851566</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.1686441589888457</v>
+        <v>0.04238006996766621</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2727,39 +2738,43 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>189</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>-449</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2224002232436589</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2317017928095088</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1588</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2860085996569768</v>
+        <v>0.2136042609009934</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1258881461697701</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.294153872982034</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -2815,34 +2830,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>39248</v>
+        <v>36105</v>
       </c>
       <c r="M6" t="n">
-        <v>1816</v>
+        <v>79</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.4569280165954954</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4634241885131012</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="P6" t="n">
-        <v>1813</v>
+        <v>77</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.2477949590837284</v>
+        <v>0.09791080322851566</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.2425136931880095</v>
+        <v>0.04238006996766621</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -2852,48 +2867,52 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4569280165954954</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4634241885131012</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1233</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.8413765220054719</v>
+        <v>0.2136042609009934</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.0520186119706062</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.0596260796301975</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
       <c r="AI6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.1371534911820741</v>
+        <v>0.003452750015039689</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.1601920858077193</v>
+        <v>-0.01304506736727939</v>
       </c>
       <c r="AL6" t="n">
-        <v>841</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -2944,66 +2963,68 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>36105</v>
+      </c>
       <c r="M7" t="n">
-        <v>1896</v>
+        <v>79</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.5165540962256929</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="P7" t="n">
-        <v>1894</v>
+        <v>77</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.2945323051586157</v>
+        <v>0.09791080322851566</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.2945323051586157</v>
+        <v>0.04238006996766621</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.03477373878520784</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.5165540962256929</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1258</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1.068483758354155</v>
+        <v>0.2136042609009934</v>
       </c>
       <c r="AF7" s="3" t="n">
         <v>0</v>
@@ -3011,9 +3032,11 @@
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -3069,66 +3092,68 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>36105</v>
+      </c>
       <c r="M8" t="n">
-        <v>1896</v>
+        <v>79</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.5165540962256929</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="P8" t="n">
-        <v>1894</v>
+        <v>77</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.2945323051586157</v>
+        <v>0.09791080322851566</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.2945323051586157</v>
+        <v>0.04238006996766621</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-0.03477373878520784</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.5165540962256929</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1258</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>1.068483758354155</v>
+        <v>0.2136042609009934</v>
       </c>
       <c r="AF8" s="3" t="n">
         <v>0</v>
@@ -3136,19 +3161,23 @@
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr"/>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
       <c r="AI8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.1891721031526803</v>
+        <v>0.003452750015039689</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.2198181654379168</v>
-      </c>
-      <c r="AL8" t="inlineStr"/>
+        <v>-0.01304506736727939</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
       <c r="AM8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
@@ -3196,83 +3225,87 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>37538</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>1896</v>
+        <v>90</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.4704102193610507</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.4767451185382657</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1894</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.3182273677443157</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.3182273677443157</v>
+        <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.1516216546398126</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>638</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-31</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.4704102193610507</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.4767451185382657</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1258</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.8882539591181335</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.02369506258569998</v>
+        <v>-0.04238006996766621</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.04614387686464227</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.1760081665685741</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-48</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.2618004968622551</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.1860700172543425</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3321,89 +3354,99 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>36105</v>
+      </c>
       <c r="M10" t="n">
-        <v>1896</v>
+        <v>79</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.5006164103140789</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.5065899861024923</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="P10" t="n">
-        <v>1894</v>
+        <v>78</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.3047304869778921</v>
+        <v>0.08993390447450868</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.3047304869778921</v>
+        <v>0.03892731995262652</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
       </c>
       <c r="U10" t="b">
-        <v>1</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>-0.08121595103414692</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.5006164103140789</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.5065899861024923</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1258</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>1.00246868470174</v>
+        <v>0.1946904599376615</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.0101981818192764</v>
+        <v>-0.003452750015039689</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.01593768591161404</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
+        <v>0.01304506736727939</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
       <c r="AI10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.1993702849719567</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.2038804795263027</v>
-      </c>
-      <c r="AL10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
       <c r="AM10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AN10" s="3" t="n">
+        <v>0.2618004968622551</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>-0.004787352809128453</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3700,68 +3743,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441404</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441404</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027499</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027499</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.5035092528573142</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286778</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2354171526922748</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1562892258388257</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459449</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.5035092528573142</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616548</v>
+        <v>0.9463998245842093</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3809,68 +3850,66 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.5164822477237522</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.522337027033672</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.2946099669213893</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.2946099669213893</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>41186</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>-0.03463028931059076</v>
+      </c>
+      <c r="W3" t="n">
+        <v>637</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.5164822477237522</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.522337027033672</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1258</v>
       </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.5129198176356868</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.514605350956002</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1255</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2233719858597075</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1508918280650655</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>355</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>-0.5129198176356868</v>
-      </c>
-      <c r="Z3" s="3" t="n">
-        <v>-0.514605350956002</v>
-      </c>
-      <c r="AA3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>903</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>43</v>
-      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1.053050064870114</v>
+        <v>1.068176391233451</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3878,11 +3917,9 @@
       <c r="AG3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
       <c r="AK3" s="3" t="inlineStr"/>
@@ -3926,34 +3963,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>38028</v>
+      </c>
+      <c r="M4" t="n">
+        <v>974</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2951492679396009</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.3383158398603918</v>
+      </c>
+      <c r="P4" t="n">
+        <v>769</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1469627184408073</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.1053877950228616</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>40956</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1099</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.4652359830536872</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.4652359830536872</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1098</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.2062376999383152</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.1302232557034226</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3963,43 +4000,39 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.2951492679396009</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>744</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-116</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.8699837092823584</v>
+        <v>0.4187401027120015</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.02066857236164291</v>
+        <v>-0.1892221718985276</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.04768383458199965</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-159</v>
-      </c>
+        <v>0.2213329797841512</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -4051,34 +4084,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>36880</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>39192</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1776</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.2222846583404645</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.2317017928095088</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1773</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1742453733805756</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1686886267623478</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>39412</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>39426</v>
-      </c>
-      <c r="M5" t="n">
-        <v>43</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.07772965305392454</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.08092115510307485</v>
-      </c>
-      <c r="P5" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.03814407642062299</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.004817010487199345</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -4088,43 +4121,39 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>33</v>
+        <v>188</v>
       </c>
       <c r="X5" t="n">
-        <v>-322</v>
+        <v>-449</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.07772965305392454</v>
+        <v>-0.2222846583404645</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.08092115510307485</v>
+        <v>-0.2317017928095088</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-850</v>
-      </c>
+        <v>1588</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.08428076790207095</v>
+        <v>0.2858175047262668</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1460748175778661</v>
+        <v>-0.1259213401590415</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.4351901645817623</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-893</v>
-      </c>
+        <v>0.2941975893832877</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -4180,34 +4209,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>39248</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1815</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.4568473066170904</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.4634241885131011</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1812</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.2478631751538404</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.2425776387664843</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>40962</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1102</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.4661136411094471</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.4679611464684285</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1099</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.2092548313031292</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1323083945908599</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -4217,52 +4246,48 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4661136411094471</v>
+        <v>-0.4568473066170904</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4679611464684285</v>
+        <v>-0.4634241885131011</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>747</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-113</v>
-      </c>
+        <v>1233</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.8730577834542514</v>
+        <v>0.8411029019698224</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.0185834334742056</v>
+        <v>-0.05203232815490497</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.04680617652623975</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-156</v>
-      </c>
+        <v>0.05963494110666179</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.002085138887437304</v>
+        <v>0.1371898437436227</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.0008776580557599001</v>
+        <v>-0.1616980386774894</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>841</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -4313,80 +4338,76 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.5164822477237522</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.522337027033672</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.2946099669213893</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.2946099669213893</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40009</v>
-      </c>
-      <c r="M7" t="n">
-        <v>444</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.27129111933142</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.2738128049668617</v>
-      </c>
-      <c r="P7" t="n">
-        <v>441</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.07607640363120459</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.03055301893498589</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>-0.03463028931059076</v>
+      </c>
       <c r="W7" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.27129111933142</v>
+        <v>-0.5164822477237522</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2738128049668617</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>89</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-771</v>
-      </c>
+        <v>1258</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.3722901237082692</v>
+        <v>1.068176391233451</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.1203388091300796</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2416286983042668</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-814</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -4442,92 +4463,86 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.5164822477237522</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.522337027033672</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.2946099669213893</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.2946099669213893</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>41107</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1202</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.4738836383842814</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.4757042557897395</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1199</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1834398430825823</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.121129697779062</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>-0.03463028931059076</v>
+      </c>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.4738836383842814</v>
+        <v>-0.5164822477237522</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.4757042557897395</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>847</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-13</v>
-      </c>
+        <v>1258</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.9007202074631759</v>
+        <v>1.068176391233451</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.02976213028600348</v>
+        <v>0</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.03903617925140546</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>-0.009093557924360576</v>
+        <v>0.1892221718985276</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.008647655330594195</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>103</v>
-      </c>
+        <v>-0.2213329797841512</v>
+      </c>
+      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
@@ -4575,80 +4590,76 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.4703315130733671</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.4767451185382658</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.3183112773827858</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.3183112773827858</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>40361</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>40487</v>
-      </c>
-      <c r="M9" t="n">
-        <v>776</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.1404817040983344</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.160491159249824</v>
-      </c>
-      <c r="P9" t="n">
-        <v>757</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.0561247974790547</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.0297844404838865</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>-0.1514955708055779</v>
+      </c>
       <c r="W9" t="n">
-        <v>688</v>
+        <v>637</v>
       </c>
       <c r="X9" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1404817040983344</v>
+        <v>-0.4703315130733671</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.160491159249824</v>
+        <v>-0.4767451185382658</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>88</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-772</v>
-      </c>
+        <v>1258</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1634423662278928</v>
+        <v>0.8879733733121167</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.121107387581179</v>
+        <v>0.02370131046139651</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3724381135373525</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-815</v>
-      </c>
+        <v>0.04615073465038511</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -4704,92 +4715,86 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.5005421931937504</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.5065899861024923</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.3048108377807462</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.3048108377807462</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>41186</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>1</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>-0.08107940368311994</v>
+      </c>
+      <c r="W10" t="n">
+        <v>637</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>-0.5005421931937504</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>-0.5065899861024923</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1258</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4661136411094471</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4679611464684285</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1255</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2075222572180686</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.140185048878466</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>355</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.4661136411094471</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.4679611464684285</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>903</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>43</v>
-      </c>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.8730577834542514</v>
+        <v>1.002171127115691</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.01070677918659951</v>
+        <v>0.01020087085935695</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.04680617652623975</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
+        <v>0.0159400545300018</v>
+      </c>
+      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.009961793175043393</v>
+        <v>0.1994230427578846</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.0008776580557599001</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>159</v>
-      </c>
+        <v>-0.2053929252541494</v>
+      </c>
+      <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" s="3" t="inlineStr"/>
       <c r="AO10" s="3" t="inlineStr"/>
@@ -5089,34 +5094,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573142</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.0826944425385638</v>
+        <v>0.2354171526922748</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.05218963375687856</v>
+        <v>0.1563175570682506</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5126,22 +5131,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573142</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5150,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160745</v>
+        <v>1.014136226616548</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5198,34 +5203,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43537</v>
+        <v>41186</v>
       </c>
       <c r="M3" t="n">
-        <v>117</v>
+        <v>1258</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.5129198176356868</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.514605350956002</v>
       </c>
       <c r="P3" t="n">
-        <v>107</v>
+        <v>1255</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.06770789437500559</v>
+        <v>0.2233719858597075</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.03909117104367223</v>
+        <v>0.1509191808846621</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5235,31 +5240,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.5129198176356868</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.514605350956002</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>53</v>
+        <v>903</v>
       </c>
       <c r="AC3" t="n">
-        <v>-23</v>
+        <v>43</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2129842038385619</v>
+        <v>1.053050064870114</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -5315,34 +5320,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43559</v>
+        <v>40956</v>
       </c>
       <c r="M4" t="n">
-        <v>133</v>
+        <v>1099</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="P4" t="n">
-        <v>131</v>
+        <v>1098</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04836031164019643</v>
+        <v>0.2062376999383152</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.02975362321475319</v>
+        <v>0.1302468618407874</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -5352,40 +5357,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>69</v>
+        <v>744</v>
       </c>
       <c r="AC4" t="n">
-        <v>-7</v>
+        <v>-116</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1715670148335215</v>
+        <v>0.8699837092823584</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.009337547828919039</v>
+        <v>-0.02067231904387468</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.02914461608744778</v>
+        <v>0.04768383458199965</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>-159</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5440,34 +5445,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>39412</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43537</v>
+        <v>39426</v>
       </c>
       <c r="M5" t="n">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1755869558437452</v>
+        <v>-0.07772965305392454</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1829503201425124</v>
+        <v>-0.08092115510307485</v>
       </c>
       <c r="P5" t="n">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.06770789437500557</v>
+        <v>0.03814407642062299</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.03909117104367222</v>
+        <v>0.004817883687693638</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -5477,40 +5482,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-322</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1755869558437452</v>
+        <v>-0.07772965305392454</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1829503201425124</v>
+        <v>-0.08092115510307485</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="AC5" t="n">
-        <v>-23</v>
+        <v>-850</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2129842038385619</v>
+        <v>0.08428076790207095</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-6.938893903907228e-18</v>
+        <v>-0.1461012971969684</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0.4351901645817623</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-893</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5569,34 +5574,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43537</v>
+        <v>40962</v>
       </c>
       <c r="M6" t="n">
-        <v>117</v>
+        <v>1102</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.4661136411094471</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.4679611464684285</v>
       </c>
       <c r="P6" t="n">
-        <v>107</v>
+        <v>1099</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.06770789437500559</v>
+        <v>0.2092548313031292</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.03909117104367223</v>
+        <v>0.1323323787104425</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -5606,52 +5611,52 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.4661136411094471</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.4679611464684285</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>53</v>
+        <v>747</v>
       </c>
       <c r="AC6" t="n">
-        <v>-23</v>
+        <v>-113</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.2129842038385619</v>
+        <v>0.8730577834542514</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0</v>
+        <v>-0.01858680217421954</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>0.04680617652623975</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-156</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.009337547828919039</v>
+        <v>0.002085516869655135</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.02914461608744778</v>
+        <v>-0.0008776580557599001</v>
       </c>
       <c r="AL6" t="n">
-        <v>-16</v>
+        <v>3</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -5702,76 +5707,80 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+        <v>39881</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>40009</v>
+      </c>
       <c r="M7" t="n">
-        <v>353</v>
+        <v>444</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.27129111933142</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.2738128049668617</v>
       </c>
       <c r="P7" t="n">
-        <v>344</v>
+        <v>441</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.09927982912619057</v>
+        <v>0.07607640363120459</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.09927982912619057</v>
+        <v>0.03055855741394646</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.0395534106461336</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.27129111933142</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.2738128049668617</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-771</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2129842038385619</v>
+        <v>0.3722901237082692</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.06018865808251835</v>
+        <v>-0.1203606234707156</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>0.2416286983042668</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-814</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -5827,34 +5836,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43635</v>
+        <v>41107</v>
       </c>
       <c r="M8" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.4738836383842814</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.4757042557897395</v>
       </c>
       <c r="P8" t="n">
-        <v>175</v>
+        <v>1199</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.06392394596506551</v>
+        <v>0.1834398430825823</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.04633598683822968</v>
+        <v>0.1211516554875319</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -5864,52 +5873,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.4738836383842814</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.4757042557897395</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>121</v>
+        <v>847</v>
       </c>
       <c r="AC8" t="n">
-        <v>45</v>
+        <v>-13</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.2129842038385619</v>
+        <v>0.9007202074631759</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.007244815794557449</v>
+        <v>-0.02976752539713021</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>0.03903617925140546</v>
       </c>
       <c r="AH8" t="n">
-        <v>68</v>
+        <v>-56</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.01658236362347649</v>
+        <v>-0.009095206353255531</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.02914461608744778</v>
+        <v>-0.008647655330594195</v>
       </c>
       <c r="AL8" t="n">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -5960,76 +5969,80 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+        <v>40361</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>40487</v>
+      </c>
       <c r="M9" t="n">
-        <v>353</v>
+        <v>776</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1755869558437456</v>
+        <v>-0.1404817040983344</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1829503201425129</v>
+        <v>-0.160491159249824</v>
       </c>
       <c r="P9" t="n">
-        <v>344</v>
+        <v>757</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.09927982912619107</v>
+        <v>0.0561247974790547</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.09927982912619107</v>
+        <v>0.02978983963928005</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.03955341064613394</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>64</v>
+        <v>688</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1755869558437456</v>
+        <v>-0.1404817040983344</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1829503201425129</v>
+        <v>-0.160491159249824</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-772</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2129842038385625</v>
+        <v>0.1634423662278928</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.06018865808251884</v>
+        <v>-0.121129341245382</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>-5.551115123125783e-16</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.3724381135373525</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-815</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -6085,34 +6098,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>43635</v>
+        <v>41186</v>
       </c>
       <c r="M10" t="n">
-        <v>185</v>
+        <v>1258</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.4661136411094471</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.4679611464684285</v>
       </c>
       <c r="P10" t="n">
-        <v>175</v>
+        <v>1255</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.06392394596506551</v>
+        <v>0.2075222572180686</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.04633598683822968</v>
+        <v>0.1402104608335154</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -6122,52 +6135,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.4661136411094471</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.4679611464684285</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>121</v>
+        <v>903</v>
       </c>
       <c r="AC10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.2129842038385619</v>
+        <v>0.8730577834542514</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.007244815794557449</v>
+        <v>-0.0107087200511467</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0</v>
+        <v>0.04680617652623975</v>
       </c>
       <c r="AH10" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.01658236362347649</v>
+        <v>0.009963598992727973</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.02914461608744778</v>
+        <v>-0.0008776580557599001</v>
       </c>
       <c r="AL10" t="n">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -6470,34 +6483,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606707</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.202297991486007</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428304</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.0521184671904906</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425156</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440424</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -6507,22 +6520,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606707</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -6531,7 +6544,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986545</v>
+        <v>0.2483971078320051</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -6579,34 +6592,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="M3" t="n">
+        <v>118</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1781636276426458</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1829503201425124</v>
+      </c>
+      <c r="P3" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.06742645627613136</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.03903818692788627</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M3" t="n">
-        <v>105</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="P3" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1345453707542304</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06362569240440749</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -6616,31 +6629,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1781636276426458</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="AC3" t="n">
-        <v>27</v>
+        <v>-25</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4537003899104699</v>
+        <v>0.2167872263083241</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6696,34 +6709,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M4" t="n">
+        <v>134</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1461536977865012</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1465009124724216</v>
+      </c>
+      <c r="P4" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.04818086645128587</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.02971168714991625</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M4" t="n">
-        <v>122</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P4" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1177175505348945</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.05996593388725459</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -6733,40 +6746,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="AC4" t="n">
-        <v>44</v>
+        <v>-9</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1711709676643378</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.003659758517152903</v>
+        <v>-0.00932649977797002</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.02185386554215096</v>
+        <v>0.03200992985614459</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -6821,34 +6834,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="M5" t="n">
+        <v>118</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1781636276426459</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1829503201425126</v>
+      </c>
+      <c r="P5" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.06742645627613136</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.03903818692788626</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M5" t="n">
-        <v>105</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="P5" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1345453707542304</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.06362569240440751</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -6858,37 +6871,37 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1781636276426459</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425126</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="AC5" t="n">
-        <v>27</v>
+        <v>-25</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4537003899104699</v>
+        <v>0.2167872263083241</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>1.387778780781446e-17</v>
+        <v>-6.938893903907228e-18</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -6950,34 +6963,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="M6" t="n">
+        <v>118</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1781636276426458</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1829503201425124</v>
+      </c>
+      <c r="P6" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.06742645627613136</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.03903818692788627</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M6" t="n">
-        <v>105</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="P6" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1345453707542304</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.06362569240440749</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -6987,31 +7000,31 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1781636276426458</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="AC6" t="n">
-        <v>27</v>
+        <v>-25</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4537003899104699</v>
+        <v>0.2167872263083241</v>
       </c>
       <c r="AF6" s="3" t="n">
         <v>0</v>
@@ -7026,13 +7039,13 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.003659758517152903</v>
+        <v>0.00932649977797002</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.02185386554215096</v>
+        <v>-0.03200992985614459</v>
       </c>
       <c r="AL6" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -7083,80 +7096,76 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>354</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1781636276426458</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1829503201425124</v>
+      </c>
+      <c r="P7" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.09914073165854347</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.09914073165854347</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M7" t="n">
-        <v>105</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="P7" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1345453707542304</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.06362569240440749</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>-0.04255525014719486</v>
+      </c>
       <c r="W7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1781636276426458</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>82</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>27</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4537003899104699</v>
+        <v>0.2167872263083241</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0</v>
+        <v>0.0601025447306572</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -7212,34 +7221,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>43636</v>
+      </c>
+      <c r="M8" t="n">
+        <v>187</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1781636276426458</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1829503201425124</v>
+      </c>
+      <c r="P8" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.06358549278462755</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.04627248139776521</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M8" t="n">
-        <v>105</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="P8" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1345453707542304</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.06362569240440749</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -7249,52 +7258,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1781636276426458</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC8" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4537003899104699</v>
+        <v>0.2167872263083241</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0</v>
+        <v>0.007234294469878937</v>
       </c>
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.003659758517152903</v>
+        <v>0.01656079424784896</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.02185386554215096</v>
+        <v>-0.03200992985614459</v>
       </c>
       <c r="AL8" t="n">
-        <v>-17</v>
+        <v>53</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -7345,80 +7354,76 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>354</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1781636276426463</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1829503201425129</v>
+      </c>
+      <c r="P9" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.09914073165854397</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.09914073165854397</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M9" t="n">
-        <v>105</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.312100342724963</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.312100342724963</v>
-      </c>
-      <c r="P9" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1345453707542306</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.06362569240440762</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>-0.04255525014719519</v>
+      </c>
       <c r="W9" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.312100342724963</v>
+        <v>-0.1781636276426463</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.312100342724963</v>
+        <v>-0.1829503201425129</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>82</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>27</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4537003899104701</v>
+        <v>0.2167872263083248</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>1.249000902703301e-16</v>
+        <v>0.06010254473065769</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>-1.110223024625157e-16</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
+        <v>-4.440892098500626e-16</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -7474,34 +7479,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>43636</v>
+      </c>
+      <c r="M10" t="n">
+        <v>187</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.1781636276426458</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.1829503201425124</v>
+      </c>
+      <c r="P10" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.06358549278462755</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.04627248139776521</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="M10" t="n">
-        <v>105</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="P10" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1345453707542304</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.06362569240440749</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -7511,52 +7516,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1781636276426458</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC10" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.4537003899104699</v>
+        <v>0.2167872263083241</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0</v>
+        <v>0.007234294469878937</v>
       </c>
       <c r="AG10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.003659758517152903</v>
+        <v>0.01656079424784896</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.02185386554215096</v>
+        <v>-0.03200992985614459</v>
       </c>
       <c r="AL10" t="n">
-        <v>-17</v>
+        <v>53</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -7859,34 +7864,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425156</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440424</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428747</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428747</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996989</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694574</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7896,22 +7901,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7920,7 +7925,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088539</v>
+        <v>0.4088864968986545</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -7968,34 +7973,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M3" t="n">
+        <v>105</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="P3" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1345453707542304</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06362569240440749</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45071</v>
-      </c>
-      <c r="M3" t="n">
-        <v>350</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3268135676014448</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3268135676014448</v>
-      </c>
-      <c r="P3" t="n">
-        <v>349</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1943317719820405</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1299458877981737</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8005,31 +8010,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AC3" t="n">
-        <v>-65</v>
+        <v>27</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4854725999705787</v>
+        <v>0.4537003899104699</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8085,34 +8090,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M4" t="n">
+        <v>122</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P4" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1177175505348945</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.05996593388725459</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45121</v>
-      </c>
-      <c r="M4" t="n">
-        <v>383</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2382824194485816</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2382824194485816</v>
-      </c>
-      <c r="P4" t="n">
-        <v>382</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1328475678049171</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.09291469197671884</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -8122,40 +8127,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="AC4" t="n">
-        <v>-32</v>
+        <v>44</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.3128225283655466</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.03703119582145487</v>
+        <v>-0.003659758517152903</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.08853114815286312</v>
+        <v>0.02185386554215096</v>
       </c>
       <c r="AH4" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8210,73 +8215,77 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M5" t="n">
+        <v>105</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="P5" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1345453707542304</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.06362569240440751</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>513</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.01059279431847393</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.0007071954500480373</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AC5" t="n">
-        <v>-220</v>
+        <v>27</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.4537003899104699</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1299458877981737</v>
+        <v>1.387778780781446e-17</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3268135676014448</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-155</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -8285,12 +8294,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.3731056573317193</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.2713930824850518</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8339,34 +8344,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M6" t="n">
+        <v>105</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="P6" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1345453707542304</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.06362569240440749</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45121</v>
-      </c>
-      <c r="M6" t="n">
-        <v>383</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="P6" t="n">
-        <v>382</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1328475678049178</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.09291469197671932</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -8376,62 +8381,58 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AC6" t="n">
-        <v>-32</v>
+        <v>27</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3128225283655484</v>
+        <v>0.4537003899104699</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.03703119582145438</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.08853114815286212</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>4.85722573273506e-16</v>
+        <v>0.003659758517152903</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>-0.02185386554215096</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.3731056573317193</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.09817014575252636</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8476,34 +8477,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M7" t="n">
+        <v>105</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="P7" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1345453707542304</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.06362569240440749</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45456</v>
-      </c>
-      <c r="M7" t="n">
-        <v>614</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.3268135676014448</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.3268135676014448</v>
-      </c>
-      <c r="P7" t="n">
-        <v>613</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.2212555704139888</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.1958379899617406</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -8513,40 +8514,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AC7" t="n">
-        <v>199</v>
+        <v>27</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4854725999705787</v>
+        <v>0.4537003899104699</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.06589210216356686</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8605,34 +8606,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M8" t="n">
+        <v>105</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="P8" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1345453707542304</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.06362569240440749</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45324</v>
-      </c>
-      <c r="M8" t="n">
-        <v>523</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.3268135676014448</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.3268135676014448</v>
-      </c>
-      <c r="P8" t="n">
-        <v>522</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1933936368859642</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1580057878682761</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -8642,52 +8643,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AC8" t="n">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4854725999705787</v>
+        <v>0.4537003899104699</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.02805990007010237</v>
+        <v>0</v>
       </c>
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.06509109589155723</v>
+        <v>0.003659758517152903</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.08853114815286312</v>
+        <v>-0.02185386554215096</v>
       </c>
       <c r="AL8" t="n">
-        <v>140</v>
+        <v>-17</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -8738,73 +8739,77 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M9" t="n">
+        <v>105</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.312100342724963</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.312100342724963</v>
+      </c>
+      <c r="P9" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1345453707542306</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.06362569240440762</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>513</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.01059279431847393</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.0007071954500480373</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0.312100342724963</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.312100342724963</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AC9" t="n">
-        <v>-220</v>
+        <v>27</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.4537003899104701</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1299458877981737</v>
+        <v>1.249000902703301e-16</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3268135676014448</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AH9" t="n">
-        <v>-155</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8863,34 +8868,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="M10" t="n">
+        <v>105</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="P10" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1345453707542304</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.06362569240440749</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45121</v>
-      </c>
-      <c r="M10" t="n">
-        <v>383</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="P10" t="n">
-        <v>382</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1328475678049178</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09291469197671932</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -8900,52 +8905,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AC10" t="n">
-        <v>-32</v>
+        <v>27</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.3128225283655484</v>
+        <v>0.4537003899104699</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.03703119582145438</v>
+        <v>0</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.08853114815286212</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>4.85722573273506e-16</v>
+        <v>0.003659758517152903</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>-0.02185386554215096</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -9248,34 +9253,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996989</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694574</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645815</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451827</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -9285,22 +9290,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -9309,7 +9314,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367012</v>
+        <v>0.4792042812088539</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -9357,34 +9362,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45071</v>
+      </c>
+      <c r="M3" t="n">
+        <v>350</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="P3" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1943317719820405</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1299458877981737</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45841</v>
-      </c>
-      <c r="M3" t="n">
-        <v>93</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.2083486754324958</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.2083486754324958</v>
-      </c>
-      <c r="P3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1010841009855249</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06637713953679047</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -9394,31 +9399,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="AC3" t="n">
-        <v>4</v>
+        <v>-65</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2631823745716855</v>
+        <v>0.4854725999705787</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -9474,34 +9479,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45121</v>
+      </c>
+      <c r="M4" t="n">
+        <v>383</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="P4" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1328475678049171</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.09291469197671884</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M4" t="n">
-        <v>108</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.1556116196127491</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.1556116196127491</v>
-      </c>
-      <c r="P4" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.06372707386676911</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.04506184607636846</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -9511,40 +9516,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="AC4" t="n">
-        <v>19</v>
+        <v>-32</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.184289153222813</v>
+        <v>0.3128225283655466</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.02131529346042202</v>
+        <v>-0.03703119582145487</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.05273705581974675</v>
+        <v>0.08853114815286312</v>
       </c>
       <c r="AH4" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9599,30 +9604,30 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
+        <v>-0.01059279431847393</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>0.0007071954500480373</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T5" t="b">
         <v>1</v>
@@ -9635,7 +9640,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y5" s="3" t="n">
         <v>0</v>
@@ -9650,7 +9655,7 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
@@ -9659,13 +9664,13 @@
         <v>0</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.06637713953679047</v>
+        <v>-0.1299458877981737</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.2083486754324958</v>
+        <v>0.3268135676014448</v>
       </c>
       <c r="AH5" t="n">
-        <v>-59</v>
+        <v>-155</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9675,10 +9680,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.02618350124865576</v>
+        <v>0.3731056573317193</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.02059674313262327</v>
+        <v>-0.2713930824850518</v>
       </c>
     </row>
     <row r="6">
@@ -9728,34 +9733,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45121</v>
+      </c>
+      <c r="M6" t="n">
+        <v>383</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="P6" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1328475678049178</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.09291469197671932</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M6" t="n">
-        <v>108</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="P6" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.06372707386676901</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.04506184607636839</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -9765,49 +9770,49 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="AC6" t="n">
-        <v>19</v>
+        <v>-32</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1842891532228128</v>
+        <v>0.3128225283655484</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.02131529346042209</v>
+        <v>-0.03703119582145438</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.05273705581974686</v>
+        <v>0.08853114815286212</v>
       </c>
       <c r="AH6" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>-6.938893903907228e-17</v>
+        <v>4.85722573273506e-16</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -9816,10 +9821,10 @@
         <v>0</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.02618350124865576</v>
+        <v>0.3731056573317193</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>0.03868077373001721</v>
+        <v>-0.09817014575252636</v>
       </c>
     </row>
     <row r="7">
@@ -9865,73 +9870,77 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45456</v>
+      </c>
+      <c r="M7" t="n">
+        <v>614</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="P7" t="n">
+        <v>613</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.2212555704139888</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.1958379899617406</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" t="n">
-        <v>88</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="X7" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>419</v>
       </c>
       <c r="AC7" t="n">
-        <v>-55</v>
+        <v>199</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0</v>
+        <v>0.4854725999705787</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.06637713953679047</v>
+        <v>0.06589210216356686</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2083486754324958</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-59</v>
+        <v>264</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -9940,12 +9949,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.02618350124865576</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>-0.02059674313262327</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9994,34 +9999,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45324</v>
+      </c>
+      <c r="M8" t="n">
+        <v>523</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="P8" t="n">
+        <v>522</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1933936368859642</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.1580057878682761</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M8" t="n">
-        <v>108</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="P8" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.06372707386676901</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.04506184607636839</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -10031,62 +10036,58 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>74</v>
+        <v>328</v>
       </c>
       <c r="AC8" t="n">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1842891532228128</v>
+        <v>0.4854725999705787</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.02131529346042209</v>
+        <v>0.02805990007010237</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.05273705581974686</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>-6.938893903907228e-17</v>
+        <v>0.06509109589155723</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-0.08853114815286312</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
       </c>
-      <c r="AN8" s="3" t="n">
-        <v>0.02618350124865576</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>0.03868077373001721</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10131,30 +10132,30 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>-0.01059279431847393</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>0.0007071954500480373</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T9" t="b">
         <v>1</v>
@@ -10167,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>0</v>
@@ -10182,7 +10183,7 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
@@ -10191,13 +10192,13 @@
         <v>0</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.06637713953679047</v>
+        <v>-0.1299458877981737</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2083486754324958</v>
+        <v>0.3268135676014448</v>
       </c>
       <c r="AH9" t="n">
-        <v>-59</v>
+        <v>-155</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10206,12 +10207,8 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.02618350124865576</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>-0.02059674313262327</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10260,34 +10257,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45121</v>
+      </c>
+      <c r="M10" t="n">
+        <v>383</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="P10" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1328475678049178</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.09291469197671932</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M10" t="n">
-        <v>108</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="P10" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.06372707386676901</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.04506184607636839</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -10297,49 +10294,49 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="AC10" t="n">
-        <v>19</v>
+        <v>-32</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.1842891532228128</v>
+        <v>0.3128225283655484</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.02131529346042209</v>
+        <v>-0.03703119582145438</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.05273705581974686</v>
+        <v>0.08853114815286212</v>
       </c>
       <c r="AH10" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>-6.938893903907228e-17</v>
+        <v>4.85722573273506e-16</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -10347,12 +10344,8 @@
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.02618350124865576</v>
-      </c>
-      <c r="AO10" s="3" t="n">
-        <v>0.03868077373001721</v>
-      </c>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10365,7 +10358,1408 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AO10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451827</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367012</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45841</v>
+      </c>
+      <c r="M3" t="n">
+        <v>93</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.2083486754324958</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.2083486754324958</v>
+      </c>
+      <c r="P3" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1010841009855249</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06637713953679047</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.2083486754324958</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.2083486754324958</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>59</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.2631823745716855</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M4" t="n">
+        <v>108</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="P4" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.06372707386676911</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.04506184607636846</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>34</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0.184289153222813</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>-0.02131529346042202</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.05273705581974675</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>89</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>-0.06637713953679047</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0.2083486754324958</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-59</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.02618350124865576</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.02059674313262327</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M6" t="n">
+        <v>108</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="P6" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.06372707386676901</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.04506184607636839</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>34</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0.1842891532228128</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.02131529346042209</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.05273705581974686</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>-6.938893903907228e-17</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="3" t="n">
+        <v>0.02618350124865576</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>0.03868077373001721</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>89</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.06637713953679047</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.2083486754324958</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-59</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.02618350124865576</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>-0.02059674313262327</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M8" t="n">
+        <v>108</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="P8" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.06372707386676901</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.04506184607636839</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>34</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0.1842891532228128</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.02131529346042209</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.05273705581974686</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="n">
+        <v>-6.938893903907228e-17</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="3" t="n">
+        <v>0.02618350124865576</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>0.03868077373001721</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>89</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>-0.06637713953679047</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.2083486754324958</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-59</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.02618350124865576</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.02059674313262327</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M10" t="n">
+        <v>108</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="P10" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.06372707386676901</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.04506184607636839</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>34</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3" t="n">
+        <v>0.1842891532228128</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>-0.02131529346042209</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>0.05273705581974686</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <v>-6.938893903907228e-17</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="3" t="n">
+        <v>0.02618350124865576</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>0.03868077373001721</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10471,12 +11865,8 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>563</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -10485,10 +11875,10 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="3" t="n">
-        <v>0.5562326869806095</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -10519,10 +11909,10 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>963</v>
+        <v>563</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -10532,7 +11922,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.9149709302325582</v>
+        <v>0.5568496949528563</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -10565,8 +11955,12 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>963</v>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
@@ -10575,10 +11969,10 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>0.9149709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -10651,24 +12045,20 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-251</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>307</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" s="3" t="n">
-        <v>0.9766081871345029</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -10699,21 +12089,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-251</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>307</v>
+      </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -10730,30 +12122,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-30</v>
+      </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -10783,15 +12177,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -10800,10 +12190,10 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" s="3" t="n">
-        <v>0.3655523255813953</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -10830,7 +12220,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -10839,16 +12229,14 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>0.5241379310344828</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -10875,11 +12263,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
@@ -10888,10 +12280,10 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>0.3655523255813953</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -10918,7 +12310,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -10930,13 +12322,13 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.4873294346978557</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -10963,22 +12355,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-30</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -10998,37 +12388,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>-193</v>
-      </c>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>57</v>
+      </c>
       <c r="J14" s="3" t="n">
-        <v>0.2770083102493075</v>
+        <v>0.4873294346978557</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -11045,37 +12433,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>209</v>
-      </c>
+        <v>-30</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.3670058139534884</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -11102,25 +12488,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-134</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.5241379310344828</v>
-      </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -11147,11 +12535,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>-193</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -11160,10 +12552,10 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0</v>
+        <v>0.2773155851358846</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -11190,14 +12582,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -11207,7 +12599,7 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.9766081871345029</v>
+        <v>0.3670058139534884</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -11237,30 +12629,165 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-30</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="3" t="n">
+        <v>0.5205479452054794</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>307</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
